--- a/documentation/Construccion y Evolucion/2. Reportes de problemas/PR 2.xlsx
+++ b/documentation/Construccion y Evolucion/2. Reportes de problemas/PR 2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\TraductorBraille\documentation\Construccion y Evolucion\2. Reportes de problemas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCAFEF5F-7017-4929-A914-D6AD7425C368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E654372-9525-4D34-A179-8707555AF619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{AAACD53E-982C-4521-B07F-7DC6290E23F5}"/>
+    <workbookView xWindow="-23136" yWindow="-1980" windowWidth="11712" windowHeight="12336" xr2:uid="{AAACD53E-982C-4521-B07F-7DC6290E23F5}"/>
   </bookViews>
   <sheets>
     <sheet name="PR Formato" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="16">
   <si>
     <t>Reporte de Problema</t>
   </si>
@@ -65,6 +65,17 @@
   </si>
   <si>
     <t xml:space="preserve"> Según SonarCloud, se ha identificado un problema significativo de código redundante en varias partes del proyecto.</t>
+  </si>
+  <si>
+    <t> El código redundante puede deberse a prácticas de desarrollo inadecuadas, falta de estandarización en el diseño, y la falta de revisiones regulares del código.</t>
+  </si>
+  <si>
+    <t>Refactorizar el código para eliminar duplicaciones y crear funciones reutilizables.
+Implementar patrones de diseño que promuevan la reutilización del código.
+Establecer un proceso de revisión de código y pruebas automatizadas para evitar la redundancia en el futuro.</t>
+  </si>
+  <si>
+    <t> Realizar una auditoría del código existente y adoptar prácticas de codificación estándar para mejorar la calidad del código y prevenir problemas similares.</t>
   </si>
 </sst>
 </file>
@@ -356,31 +367,31 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -717,7 +728,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F84A08-0160-4953-9528-DB07A5F993CD}">
   <dimension ref="B1:H28"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="5.5703125" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -976,7 +987,7 @@
         <v>8</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D18" s="22"/>
       <c r="E18" s="22"/>
@@ -1032,7 +1043,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
@@ -1042,7 +1053,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
@@ -1091,12 +1102,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D26" s="28"/>
       <c r="E26" s="28"/>
